--- a/data/experimental_points.xlsx
+++ b/data/experimental_points.xlsx
@@ -2045,7 +2045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O36"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2516,705 +2516,927 @@
         <v>411.05</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>геометрия Barbour, с дрейфом</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" t="n">
+        <v>60</v>
+      </c>
+      <c r="D11" t="n">
+        <v>54.41</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.046</v>
+      </c>
+      <c r="F11" t="n">
+        <v>70.41</v>
+      </c>
+      <c r="G11" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="H11" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="J11" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="L11" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="M11" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>687.2 (проверка)</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>361.4 (проверка)</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>геометрия Barbour, Ω = 0</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" t="n">
+        <v>60</v>
+      </c>
+      <c r="D12" t="n">
+        <v>85.06</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.605</v>
+      </c>
+      <c r="F12" t="n">
+        <v>99.06</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="H12" t="n">
+        <v>22.35</v>
+      </c>
+      <c r="I12" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="J12" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="K12" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="L12" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="M12" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>549.8 (проверка)</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>412.4 (проверка)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Параметры</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>параметр</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>исходная модель (config.py)</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>единая модель (основной результат)</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>единая, без дрейфа</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>единая, дрейф только в щели</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>единая, a и захват из литературы</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>единая, D_cleft = 330 (измеренный)</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>единая, AMPA включён в подгонку</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>cleft_radius_nm</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>249.7 (fit)</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>98.38 (fit)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>224 (fit)</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>84.22 (fit)</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>249.7 (fit)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>D_cleft</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>16.72 (fit)</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>5.473 (fit)</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>36.74 (fit)</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>12.9 (fit)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>15.43 (fit)</t>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>геометрия Barbour, с дрейфом</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>геометрия Barbour, Ω = 0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D_pm</t>
+          <t>cleft_radius_nm</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>249.7 (fit)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>98.38 (fit)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>224 (fit)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>84.22 (fit)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>249.7 (fit)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>250 (fit)</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>174.7 (fit)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>omega_scale</t>
+          <t>D_cleft</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.675 (fit)</t>
+          <t>16.72 (fit)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.473 (fit)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>-7.997 (fit)</t>
+          <t>36.74 (fit)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-1.253 (fit)</t>
+          <t>12.9 (fit)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-2.266 (fit)</t>
+          <t>330</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.669 (fit)</t>
+          <t>15.43 (fit)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>18.67 (fit)</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>13.23 (fit)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>omega_pm_ratio</t>
+          <t>D_pm</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>320</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>320</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>320</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>320</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>320</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>320</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Vmax_pm</t>
+          <t>omega_scale</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>-1.675 (fit)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>3.645e-05 (fit)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>0.0001811 (fit)</t>
-        </is>
-      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.148e-05 (fit)</t>
+          <t>-7.997 (fit)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.0036</t>
+          <t>-1.253 (fit)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.0001127 (fit)</t>
+          <t>-2.266 (fit)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6.044e-05 (fit)</t>
+          <t>-1.669 (fit)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-1.661 (fit)</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Km</t>
+          <t>omega_pm_ratio</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>molecules</t>
+          <t>Vmax_pm</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3028 (fit)</t>
+          <t>3.645e-05 (fit)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4785 (fit)</t>
+          <t>0.0001811 (fit)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>7200 (fit)</t>
+          <t>1.148e-05 (fit)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>5664 (fit)</t>
+          <t>0.0036</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1e+04 (fit)</t>
+          <t>0.0001127 (fit)</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2277 (fit)</t>
+          <t>6.044e-05 (fit)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3.646e-05 (fit)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1.046e-05 (fit)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>psf_xy_um</t>
+          <t>Km</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.6985 (fit)</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.6919 (fit)</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.6995 (fit)</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.6999 (fit)</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.3161 (fit)</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.6994 (fit)</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>psf_z_um</t>
+          <t>molecules</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.291 (fit)</t>
+          <t>3028 (fit)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3.305 (fit)</t>
+          <t>4785 (fit)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2.588 (fit)</t>
+          <t>7200 (fit)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>3.281 (fit)</t>
+          <t>5664 (fit)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.089 (fit)</t>
+          <t>1e+04 (fit)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.73 (fit)</t>
+          <t>2277 (fit)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3011 (fit)</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>6143 (fit)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>uncaging_molecules</t>
+          <t>psf_xy_um</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3.6e+04</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.805e+05 (fit)</t>
+          <t>0.6985 (fit)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.562e+05 (fit)</t>
+          <t>0.6919 (fit)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.541e+05 (fit)</t>
+          <t>0.6995 (fit)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2.847e+05 (fit)</t>
+          <t>0.6999 (fit)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.092e+05 (fit)</t>
+          <t>0.3161 (fit)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.584e+05 (fit)</t>
+          <t>0.6994 (fit)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0.7 (fit)</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0.6993 (fit)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>alpha</t>
+          <t>psf_z_um</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.291 (fit)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>3.305 (fit)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>2.588 (fit)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>3.281 (fit)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.089 (fit)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.73 (fit)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1.285 (fit)</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2.378 (fit)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cleft_height_nm</t>
+          <t>uncaging_molecules</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3.6e+04</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1.805e+05 (fit)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1.562e+05 (fit)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1.541e+05 (fit)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2.847e+05 (fit)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2.092e+05 (fit)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1.584e+05 (fit)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1.805e+05 (fit)</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>1.579e+05 (fit)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>alpha</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cleft_height_nm</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>transition_width_nm</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Проверки без подгонки</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>исходная модель (config.py)</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>время захвата, мс: None (Diamond 2005: 0,75 ± 0,15 при 35 °C)</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>щель, мМ при 0,5/1/2/4 мс: 0.0384 / 0.0237 / 0.009 / 0.00129 (Clements Fig. 3C: ~0,7 / 0,5 / 0,22 при 0,6/1/2,4 мс)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>единая модель (основной результат)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>время захвата, мс: inf (Diamond 2005: 0,75 ± 0,15 при 35 °C)</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>щель, мМ при 0,5/1/2/4 мс: 1.05 / 0.675 / 0.275 / 0.0481 (Clements Fig. 3C: ~0,7 / 0,5 / 0,22 при 0,6/1/2,4 мс)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>единая, без дрейфа</t>
+          <t>исходная модель (config.py)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>время захвата, мс: inf (Diamond 2005: 0,75 ± 0,15 при 35 °C)</t>
+          <t>время захвата, мс: None (Diamond 2005: 0,75 ± 0,15 при 35 °C)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>щель, мМ при 0,5/1/2/4 мс: 5.37 / 1.77 / 0.198 / 0.00357 (Clements Fig. 3C: ~0,7 / 0,5 / 0,22 при 0,6/1/2,4 мс)</t>
+          <t>щель, мМ при 0,5/1/2/4 мс: 0.0384 / 0.0237 / 0.009 / 0.00129 (Clements Fig. 3C: ~0,7 / 0,5 / 0,22 при 0,6/1/2,4 мс)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>единая, дрейф только в щели</t>
+          <t>единая модель (основной результат)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3224,31 +3446,31 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>щель, мМ при 0,5/1/2/4 мс: 2.16 / 1.08 / 0.291 / 0.0287 (Clements Fig. 3C: ~0,7 / 0,5 / 0,22 при 0,6/1/2,4 мс)</t>
+          <t>щель, мМ при 0,5/1/2/4 мс: 1.05 / 0.675 / 0.275 / 0.0481 (Clements Fig. 3C: ~0,7 / 0,5 / 0,22 при 0,6/1/2,4 мс)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>единая, a и захват из литературы</t>
+          <t>единая, без дрейфа</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>время захвата, мс: 6.42 (Diamond 2005: 0,75 ± 0,15 при 35 °C)</t>
+          <t>время захвата, мс: inf (Diamond 2005: 0,75 ± 0,15 при 35 °C)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>щель, мМ при 0,5/1/2/4 мс: 3.17 / 1.19 / 0.176 / 0.00707 (Clements Fig. 3C: ~0,7 / 0,5 / 0,22 при 0,6/1/2,4 мс)</t>
+          <t>щель, мМ при 0,5/1/2/4 мс: 5.37 / 1.77 / 0.198 / 0.00357 (Clements Fig. 3C: ~0,7 / 0,5 / 0,22 при 0,6/1/2,4 мс)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>единая, D_cleft = 330 (измеренный)</t>
+          <t>единая, дрейф только в щели</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3258,24 +3480,92 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>щель, мМ при 0,5/1/2/4 мс: 0.0509 / 0.0239 / 0.0123 / 0.00715 (Clements Fig. 3C: ~0,7 / 0,5 / 0,22 при 0,6/1/2,4 мс)</t>
+          <t>щель, мМ при 0,5/1/2/4 мс: 2.16 / 1.08 / 0.291 / 0.0287 (Clements Fig. 3C: ~0,7 / 0,5 / 0,22 при 0,6/1/2,4 мс)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>единая, a и захват из литературы</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>время захвата, мс: 6.42 (Diamond 2005: 0,75 ± 0,15 при 35 °C)</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>щель, мМ при 0,5/1/2/4 мс: 3.17 / 1.19 / 0.176 / 0.00707 (Clements Fig. 3C: ~0,7 / 0,5 / 0,22 при 0,6/1/2,4 мс)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>единая, D_cleft = 330 (измеренный)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>время захвата, мс: inf (Diamond 2005: 0,75 ± 0,15 при 35 °C)</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>щель, мМ при 0,5/1/2/4 мс: 0.0509 / 0.0239 / 0.0123 / 0.00715 (Clements Fig. 3C: ~0,7 / 0,5 / 0,22 при 0,6/1/2,4 мс)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>единая, AMPA включён в подгонку</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>время захвата, мс: inf (Diamond 2005: 0,75 ± 0,15 при 35 °C)</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>щель, мМ при 0,5/1/2/4 мс: 0.815 / 0.555 / 0.248 / 0.0515 (Clements Fig. 3C: ~0,7 / 0,5 / 0,22 при 0,6/1/2,4 мс)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>геометрия Barbour, с дрейфом</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>время захвата, мс: inf (Diamond 2005: 0,75 ± 0,15 при 35 °C)</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>щель, мМ при 0,5/1/2/4 мс: 1.05 / 0.688 / 0.285 / 0.0513 (Clements Fig. 3C: ~0,7 / 0,5 / 0,22 при 0,6/1/2,4 мс)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>геометрия Barbour, Ω = 0</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>время захвата, мс: inf (Diamond 2005: 0,75 ± 0,15 при 35 °C)</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>щель, мМ при 0,5/1/2/4 мс: 3.22 / 1.4 / 0.262 / 0.0106 (Clements Fig. 3C: ~0,7 / 0,5 / 0,22 при 0,6/1/2,4 мс)</t>
         </is>
       </c>
     </row>
